--- a/tests/workbooktests/workbooks/test_stochasticprocess.xlsx
+++ b/tests/workbooktests/workbooks/test_stochasticprocess.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B804ED3F-7F6A-4DEA-B5E6-17B0C0E8CCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F967E81-9B61-417A-8653-FE86C21F3EAA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" activeTab="2" xr2:uid="{536DAD22-F64C-4E0C-9C73-53C6A08A9B53}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{536DAD22-F64C-4E0C-9C73-53C6A08A9B53}"/>
   </bookViews>
   <sheets>
     <sheet name="qlStochasticProcess(1D)" sheetId="1" r:id="rId1"/>
@@ -22,17 +22,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -41,14 +30,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -474,7 +463,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -538,7 +527,7 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -871,13 +860,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F373020B-96A1-4AED-B897-7871E86B1E67}">
   <dimension ref="A1:C58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="35.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="35.75" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -885,7 +874,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -893,7 +882,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -901,7 +890,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -912,7 +901,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="B6">
         <v>0.2</v>
       </c>
@@ -920,94 +909,94 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" t="e" cm="1">
-        <f t="array" aca="1" ref="B8" ca="1">_xll.qlGeometricBrownianMotionProcess(B1,B2,B3)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B9" t="e" cm="1">
-        <f t="array" aca="1" ref="B9" ca="1">_xll.qlGeometricBrownianMotionProcess(B1,B2,B3)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B8" t="str">
+        <f t="array" ref="B8">_xll.qlGeometricBrownianMotionProcess(B1,B2,B3)</f>
+        <v>欣[test_stochasticprocess.xlsx]qlStochasticProcess(1D)!R8C2GeometricBrownianMotionProcess,A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" t="str">
+        <f t="array" ref="B9">_xll.qlGeometricBrownianMotionProcess(B1,B2,B3)</f>
+        <v>欣[test_stochasticprocess.xlsx]qlStochasticProcess(1D)!R9C2GeometricBrownianMotionProcess,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="B11" t="e" cm="1">
-        <f t="array" aca="1" ref="B11" ca="1">_xll.qlStochasticProcessArray(B8,B5)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B11" t="str">
+        <f t="array" ref="B11">_xll.qlStochasticProcessArray(B8,B5)</f>
+        <v>欣[test_stochasticprocess.xlsx]qlStochasticProcess(1D)!R11C2StochasticProcessArray,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
-      <c r="B12" t="e" cm="1">
-        <f t="array" aca="1" ref="B12" ca="1">_xll.qlStochasticProcessArray(B8:B9,B5:C6)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B12" t="str">
+        <f t="array" ref="B12">_xll.qlStochasticProcessArray(B8:B9,B5:C6)</f>
+        <v>欣[test_stochasticprocess.xlsx]qlStochasticProcess(1D)!R12C2StochasticProcessArray,A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
-      <c r="B14" t="e" cm="1">
-        <f t="array" aca="1" ref="B14" ca="1">_xll.qlStochasticProcessSize(B8)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <f t="array" ref="B14">_xll.qlStochasticProcessSize(B8)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
-      <c r="B15" t="e" cm="1">
-        <f t="array" aca="1" ref="B15" ca="1">_xll.qlStochasticProcessSize(B12)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <f t="array" ref="B15">_xll.qlStochasticProcessSize(B12)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>7</v>
       </c>
-      <c r="B17" t="e" cm="1">
-        <f t="array" aca="1" ref="B17" ca="1">_xll.qlStochasticProcessFactors(B8)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <f t="array" ref="B17">_xll.qlStochasticProcessFactors(B8)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>7</v>
       </c>
-      <c r="B18" t="e" cm="1">
-        <f t="array" aca="1" ref="B18" ca="1">_xll.qlStochasticProcessFactors(B12)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <f t="array" ref="B18">_xll.qlStochasticProcessFactors(B12)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>8</v>
       </c>
-      <c r="B20" t="e" cm="1">
-        <f t="array" aca="1" ref="B20" ca="1">_xll.qlStochasticProcessInitialValues(B8)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <f t="array" ref="B20">_xll.qlStochasticProcessInitialValues(B8)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>8</v>
       </c>
-      <c r="B21" t="e" cm="1">
-        <f t="array" aca="1" ref="B21" ca="1">TRANSPOSE(_xll.qlStochasticProcessInitialValues(B12))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <f t="array" ref="B21">TRANSPOSE(_xll.qlStochasticProcessInitialValues(B12))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1015,7 +1004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -1024,199 +1013,199 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>9</v>
       </c>
-      <c r="B26" t="e" cm="1">
-        <f t="array" aca="1" ref="B26" ca="1">_xll.qlStochasticProcessDrift(B11,B23,B24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <f t="array" ref="B26">_xll.qlStochasticProcessDrift(B11,B23,B24)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>9</v>
       </c>
-      <c r="B27" t="e" cm="1">
+      <c r="B27">
         <f t="array" aca="1" ref="B27" ca="1">TRANSPOSE(_xll.qlStochasticProcessDrift(B12,B23,_xlfn.ANCHORARRAY(B21)))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-107341312.95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>12</v>
       </c>
-      <c r="B29" t="e" cm="1">
-        <f t="array" aca="1" ref="B29" ca="1">_xll.qlStochasticProcessDiffusion(B11,B23,B20)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <f t="array" ref="B29">_xll.qlStochasticProcessDiffusion(B11,B23,B20)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>12</v>
       </c>
-      <c r="B30" t="e" cm="1">
+      <c r="B30">
         <f t="array" aca="1" ref="B30" ca="1">_xll.qlStochasticProcessDiffusion(B12,B23,_xlfn.ANCHORARRAY(B21))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-332584893.93231082</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>13</v>
       </c>
-      <c r="B33" t="e" cm="1">
-        <f t="array" aca="1" ref="B33" ca="1">_xll.qlStochasticProcessExpectation(B11,0,B20,B23)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <f t="array" ref="B33">_xll.qlStochasticProcessExpectation(B11,0,B20,B23)</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>13</v>
       </c>
-      <c r="B34" t="e" cm="1">
+      <c r="B34">
         <f t="array" aca="1" ref="B34" ca="1">TRANSPOSE(_xll.qlStochasticProcessExpectation(B12,0,_xlfn.ANCHORARRAY(B21),B23))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-2361508884.9000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>14</v>
       </c>
-      <c r="B36" t="e" cm="1">
-        <f t="array" aca="1" ref="B36" ca="1">_xll.qlStochasticProcessStdDeviation(B11,0,B20,B23)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <f t="array" ref="B36">_xll.qlStochasticProcessStdDeviation(B11,0,B20,B23)</f>
+        <v>28.284271247461902</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>14</v>
       </c>
-      <c r="B37" t="e" cm="1">
+      <c r="B37">
         <f t="array" aca="1" ref="B37" ca="1">_xll.qlStochasticProcessStdDeviation(B12,0,_xlfn.ANCHORARRAY(B21),B23)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-470346067.63949126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>15</v>
       </c>
-      <c r="B40" t="e" cm="1">
-        <f t="array" aca="1" ref="B40" ca="1">_xll.qlStochasticProcessCovariance(B11,0,B20,B23)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <f t="array" ref="B40">_xll.qlStochasticProcessCovariance(B11,0,B20,B23)</f>
+        <v>800.00000000000011</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>15</v>
       </c>
-      <c r="B41" t="e" cm="1">
+      <c r="B41">
         <f t="array" aca="1" ref="B41" ca="1">_xll.qlStochasticProcessCovariance(B12,0,_xlfn.ANCHORARRAY(B21),B23)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3.6870903890655488E+17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>16</v>
       </c>
       <c r="B44">
         <f ca="1">2*(RAND()-0.5)</f>
-        <v>0.6926657892061725</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.18331920132897173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="B45">
         <f ca="1">2*(RAND()-0.5)</f>
-        <v>0.86808509225713104</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.30005456652867779</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>17</v>
       </c>
-      <c r="B47" t="e" cm="1">
+      <c r="B47">
         <f t="array" aca="1" ref="B47" ca="1">_xll.qlStochasticProcessEvolve(B11,0,B20,B23,B44)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>115.18505001525672</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>17</v>
       </c>
-      <c r="B48" t="e" cm="1">
+      <c r="B48">
         <f t="array" aca="1" ref="B48" ca="1">TRANSPOSE(_xll.qlStochasticProcessEvolve(B12,0,_xlfn.ANCHORARRAY(B21),B23,B44:B45))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-2332500608.0347495</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>18</v>
       </c>
-      <c r="B51" t="e" cm="1">
-        <f t="array" aca="1" ref="B51" ca="1">_xll.qlStochasticProcess1DX0(B8)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <f t="array" ref="B51">_xll.qlStochasticProcess1DX0(B8)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>19</v>
       </c>
-      <c r="B52" t="e" cm="1">
-        <f t="array" aca="1" ref="B52" ca="1">_xll.qlStochasticProcess1DDrift(B8,B23,B24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B52">
+        <f t="array" ref="B52">_xll.qlStochasticProcess1DDrift(B8,B23,B24)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>20</v>
       </c>
-      <c r="B53" t="e" cm="1">
-        <f t="array" aca="1" ref="B53" ca="1">_xll.qlStochasticProcess1DDiffusion(B8,B23,B24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B53">
+        <f t="array" ref="B53">_xll.qlStochasticProcess1DDiffusion(B8,B23,B24)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>21</v>
       </c>
-      <c r="B54" t="e" cm="1">
-        <f t="array" aca="1" ref="B54" ca="1">_xll.qlStochasticProcess1DExpectation(B8,0,B20,B23)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B54">
+        <f t="array" ref="B54">_xll.qlStochasticProcess1DExpectation(B8,0,B20,B23)</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>22</v>
       </c>
-      <c r="B55" t="e" cm="1">
-        <f t="array" aca="1" ref="B55" ca="1">_xll.qlStochasticProcess1DStdDeviation(B8,0,B20,B23)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B55">
+        <f t="array" ref="B55">_xll.qlStochasticProcess1DStdDeviation(B8,0,B20,B23)</f>
+        <v>28.284271247461902</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>23</v>
       </c>
-      <c r="B56" t="e" cm="1">
-        <f t="array" aca="1" ref="B56" ca="1">_xll.qlStochasticProcess1DVariance(B8,0,B20,B23)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B56">
+        <f t="array" ref="B56">_xll.qlStochasticProcess1DVariance(B8,0,B20,B23)</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>24</v>
       </c>
-      <c r="B57" t="e" cm="1">
+      <c r="B57">
         <f t="array" aca="1" ref="B57" ca="1">_xll.qlStochasticProcess1DEvolve(B8,0,B20,B23,B44)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+        <v>115.18505001525672</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>25</v>
       </c>
-      <c r="B58" t="e" cm="1">
-        <f t="array" aca="1" ref="B58" ca="1">_xll.qlStochasticProcess1DApply(B8,B20,B52)</f>
-        <v>#VALUE!</v>
+      <c r="B58">
+        <f t="array" ref="B58">_xll.qlStochasticProcess1DApply(B8,B20,B52)</f>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1227,13 +1216,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF463D5A-8059-46B7-9FB0-FDD57B429219}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="41.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" customWidth="1"/>
+    <col min="1" max="1" width="41.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1241,16 +1230,16 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" cm="1">
+        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1258,7 +1247,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1266,7 +1255,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -1274,175 +1263,175 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="B6" s="4"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" t="e" cm="1">
-        <f t="array" aca="1" ref="B7" ca="1">_xll.qlFlatForward(B1,0.03)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"actual365fixed")</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R7C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="e" cm="1">
-        <f t="array" aca="1" ref="B8" ca="1">_xll.qlFlatForward(B1,0.02)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="str">
+        <f>_xll.qlFlatForward(B1,0.02,"actual365fixed")</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R8C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="e" cm="1">
-        <f t="array" aca="1" ref="B9" ca="1">_xll.qlBlackConstantVol(B2,"NullCalendar",B3,B5)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" t="str" cm="1">
+        <f t="array" ref="B9">_xll.qlBlackConstantVol(B2,"NullCalendar",B3,B5)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R9C2BlackVolTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="e" cm="1">
-        <f t="array" aca="1" ref="B10" ca="1">_xll.qlLocalConstantVol(B2,B3+0.05,B5)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" t="str" cm="1">
+        <f t="array" ref="B10">_xll.qlLocalConstantVol(B2,B3+0.05,B5)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R10C2LocalVolTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>31</v>
       </c>
-      <c r="B12" t="e" cm="1">
-        <f t="array" aca="1" ref="B12" ca="1">_xll.qlGeneralizedBlackScholesProcess(B4,B7,B8,B9)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" t="str" cm="1">
+        <f t="array" ref="B12">_xll.qlGeneralizedBlackScholesProcess(B4,B7,B8,B9)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R12C2GeneralizedBlackScholesProcess,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>45</v>
       </c>
-      <c r="B13" t="e" cm="1">
-        <f t="array" aca="1" ref="B13" ca="1">_xll.qlGeneralizedBlackScholesProcess(B4,B7,B8,B9,B10)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" t="str" cm="1">
+        <f t="array" ref="B13">_xll.qlGeneralizedBlackScholesProcess(B4,B7,B8,B9,B10)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R13C2GeneralizedBlackScholesProcess,A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="B15" t="e" cm="1">
-        <f t="array" aca="1" ref="B15" ca="1">_xll.qlGeneralizedBlackScholesProcessStateVariable(B12)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15" cm="1">
+        <f t="array" ref="B15">_xll.qlGeneralizedBlackScholesProcessStateVariable(B12)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>33</v>
       </c>
-      <c r="B16" t="e" cm="1">
-        <f t="array" aca="1" ref="B16" ca="1">_xll.qlGeneralizedBlackScholesProcessDividendYield(B12)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B16" t="str" cm="1">
+        <f t="array" ref="B16">_xll.qlGeneralizedBlackScholesProcessDividendYield(B12)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R16C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
         <v>34</v>
       </c>
-      <c r="B17" t="e" cm="1">
-        <f t="array" aca="1" ref="B17" ca="1">_xll.qlGeneralizedBlackScholesProcessRiskFreeRate(B12)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B17" t="str" cm="1">
+        <f t="array" ref="B17">_xll.qlGeneralizedBlackScholesProcessRiskFreeRate(B12)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R17C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>35</v>
       </c>
-      <c r="B18" t="e" cm="1">
-        <f t="array" aca="1" ref="B18" ca="1">_xll.qlGeneralizedBlackScholesProcessBlackVolatility(B12)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B18" t="str" cm="1">
+        <f t="array" ref="B18">_xll.qlGeneralizedBlackScholesProcessBlackVolatility(B12)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R18C2BlackVolTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B19" ca="1">_xll.qlGeneralizedBlackScholesProcessLocalVolatility(B12)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L19" t="e" cm="1">
-        <f t="array" aca="1" ref="L19" ca="1">_xll.qlLocalVolTermStructureLocalVol(B19,B1+1,B4)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="str" cm="1">
+        <f t="array" ref="B19">_xll.qlGeneralizedBlackScholesProcessLocalVolatility(B12)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R19C2LocalVolTermStructureHandle,A</v>
+      </c>
+      <c r="L19" cm="1">
+        <f t="array" ref="L19">_xll.qlLocalVolTermStructureLocalVol(B19,B1+1,B4)</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B20" ca="1">_xll.qlGeneralizedBlackScholesProcessLocalVolatility(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L20" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="L20" ca="1">_xll.qlLocalVolTermStructureLocalVol(B20,B2+1,B4)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="str" cm="1">
+        <f t="array" ref="B20">_xll.qlGeneralizedBlackScholesProcessLocalVolatility(B13)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R20C2LocalVolTermStructureHandle,A</v>
+      </c>
+      <c r="L20" s="2" cm="1">
+        <f t="array" ref="L20">_xll.qlLocalVolTermStructureLocalVol(B20,B2+1,B4)</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>37</v>
       </c>
-      <c r="B22" t="e" cm="1">
-        <f t="array" aca="1" ref="B22" ca="1">_xll.qlBlackScholesProcess(B4,B8,B9)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K22" t="e" cm="1">
-        <f t="array" aca="1" ref="K22" ca="1">_xll.qlStochasticProcess1DX0(B22)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B22" t="str" cm="1">
+        <f t="array" ref="B22">_xll.qlBlackScholesProcess(B4,B8,B9)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R22C2BlackScholesProcess,A</v>
+      </c>
+      <c r="K22" cm="1">
+        <f t="array" ref="K22">_xll.qlStochasticProcess1DX0(B22)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>38</v>
       </c>
-      <c r="B23" t="e" cm="1">
-        <f t="array" aca="1" ref="B23" ca="1">_xll.qlBlackScholesMertonProcess(B4,B7,B8,B9)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K23" t="e" cm="1">
-        <f t="array" aca="1" ref="K23" ca="1">_xll.qlStochasticProcess1DX0(B23)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B23" t="str" cm="1">
+        <f t="array" ref="B23">_xll.qlBlackScholesMertonProcess(B4,B7,B8,B9)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R23C2BlackScholesMertonProcess,A</v>
+      </c>
+      <c r="K23" cm="1">
+        <f t="array" ref="K23">_xll.qlStochasticProcess1DX0(B23)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" t="e" cm="1">
-        <f t="array" aca="1" ref="B24" ca="1">_xll.qlBlackProcess(B4,B8,B9)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K24" t="e" cm="1">
-        <f t="array" aca="1" ref="K24" ca="1">_xll.qlStochasticProcess1DX0(B24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B24" t="str" cm="1">
+        <f t="array" ref="B24">_xll.qlBlackProcess(B4,B8,B9)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R24C2BlackProcess,A</v>
+      </c>
+      <c r="K24" cm="1">
+        <f t="array" ref="K24">_xll.qlStochasticProcess1DX0(B24)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
         <v>40</v>
       </c>
-      <c r="B25" t="e" cm="1">
-        <f t="array" aca="1" ref="B25" ca="1">_xll.qlGarmanKohlagenProcess(B4,B7,B8,B9)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K25" t="e" cm="1">
-        <f t="array" aca="1" ref="K25" ca="1">_xll.qlStochasticProcess1DX0(B25)</f>
-        <v>#VALUE!</v>
+      <c r="B25" t="str" cm="1">
+        <f t="array" ref="B25">_xll.qlGarmanKohlagenProcess(B4,B7,B8,B9)</f>
+        <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R25C2GarmanKohlagenProcess,A</v>
+      </c>
+      <c r="K25" cm="1">
+        <f t="array" ref="K25">_xll.qlStochasticProcess1DX0(B25)</f>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1453,13 +1442,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{295C3676-83DD-40B3-9B89-D288ED5DA16F}">
   <dimension ref="A1:F114"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="35.33203125" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" customWidth="1"/>
+    <col min="1" max="1" width="35.375" customWidth="1"/>
+    <col min="2" max="2" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1467,16 +1456,16 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" cm="1">
+        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -1484,34 +1473,34 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="e" cm="1">
-        <f t="array" aca="1" ref="B6" ca="1">_xll.qlFlatForward($B$2,0.03)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" t="str">
+        <f>_xll.qlFlatForward($B$2,0.03,"actual365fixed")</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R6C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="e" cm="1">
-        <f t="array" aca="1" ref="B7" ca="1">_xll.qlFlatForward($B$2,0.02)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" t="str">
+        <f>_xll.qlFlatForward($B$2,0.02,"actual365fixed")</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R7C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>47</v>
       </c>
-      <c r="B8" t="e" cm="1">
-        <f t="array" aca="1" ref="B8" ca="1">_xll.qlBlackConstantVol(B2,"NullCalendar",0.25,"Act/365")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" t="str" cm="1">
+        <f t="array" ref="B8">_xll.qlBlackConstantVol(B2,"NullCalendar",0.25,"Act/365")</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R8C2BlackVolTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -1519,7 +1508,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -1527,7 +1516,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -1535,25 +1524,25 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15">
       <c r="A13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="e" cm="1">
-        <f t="array" aca="1" ref="B13" ca="1">_xll.qlMerton76Process(B5,B6,B7,B8,B10,B11,B12)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" t="str" cm="1">
+        <f t="array" ref="B13">_xll.qlMerton76Process(B5,B6,B7,B8,B10,B11,B12)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R13C2Merton76Process,A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" t="e" cm="1">
-        <f t="array" aca="1" ref="B14" ca="1">_xll.qlStochasticProcessInitialValues(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14" cm="1">
+        <f t="array" ref="B14">_xll.qlStochasticProcessInitialValues(B13)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1564,7 +1553,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>52</v>
       </c>
@@ -1572,7 +1561,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -1580,25 +1569,25 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="15">
       <c r="A19" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B19" t="e" cm="1">
-        <f t="array" aca="1" ref="B19" ca="1">_xll.qlVarianceGammaProcess(B5,B6,B7,B16,B17,B18)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B19" t="str" cm="1">
+        <f t="array" ref="B19">_xll.qlVarianceGammaProcess(B5,B6,B7,B16,B17,B18)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R19C2VarianceGammaProcess,A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>8</v>
       </c>
-      <c r="B20" t="e" cm="1">
-        <f t="array" aca="1" ref="B20" ca="1">_xll.qlStochasticProcessInitialValues(B19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B20" cm="1">
+        <f t="array" ref="B20">_xll.qlStochasticProcessInitialValues(B19)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1606,7 +1595,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1614,7 +1603,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1622,7 +1611,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -1630,7 +1619,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1638,7 +1627,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -1646,43 +1635,43 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="15">
       <c r="A28" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B28" t="e" cm="1">
-        <f t="array" aca="1" ref="B28" ca="1">_xll.qlHestonProcess(B7,B6,B5,B22,B23,B24,B25,B26,B27)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B28" t="str" cm="1">
+        <f t="array" ref="B28">_xll.qlHestonProcess(B7,B6,B5,B22,B23,B24,B25,B26,B27)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R28C2HestonProcess,A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>62</v>
       </c>
-      <c r="B29" t="e" cm="1">
-        <f t="array" aca="1" ref="B29" ca="1">_xll.qlHestonProcessS0(B28)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B29" cm="1">
+        <f t="array" ref="B29">_xll.qlHestonProcessS0(B28)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>63</v>
       </c>
-      <c r="B30" t="e" cm="1">
-        <f t="array" aca="1" ref="B30" ca="1">_xll.qlHestonProcessRiskFreeRate(B28)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B30" t="str" cm="1">
+        <f t="array" ref="B30">_xll.qlHestonProcessRiskFreeRate(B28)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R30C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>64</v>
       </c>
-      <c r="B31" t="e" cm="1">
-        <f t="array" aca="1" ref="B31" ca="1">_xll.qlHestonProcessDividendYield(B28)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B31" t="str" cm="1">
+        <f t="array" ref="B31">_xll.qlHestonProcessDividendYield(B28)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R31C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1693,7 +1682,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>57</v>
       </c>
@@ -1704,7 +1693,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>53</v>
       </c>
@@ -1715,7 +1704,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>1</v>
       </c>
@@ -1726,7 +1715,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>58</v>
       </c>
@@ -1737,7 +1726,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>73</v>
       </c>
@@ -1748,7 +1737,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -1759,7 +1748,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -1770,25 +1759,25 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="15">
       <c r="A41" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B41" t="e" cm="1">
-        <f t="array" aca="1" ref="B41" ca="1">_xll.qlBatesProcess(B7,B6,B5,B33,B34,B35,B36,B37,B38,B39,B40)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B41" t="str" cm="1">
+        <f t="array" ref="B41">_xll.qlBatesProcess(B7,B6,B5,B33,B34,B35,B36,B37,B38,B39,B40)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R41C2BatesProcess,A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>8</v>
       </c>
-      <c r="B42" t="e" cm="1">
-        <f t="array" aca="1" ref="B42" ca="1">_xll.qlStochasticProcessInitialValues(B41)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B42" cm="1">
+        <f t="array" ref="B42">_xll.qlStochasticProcessInitialValues(B41)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>76</v>
       </c>
@@ -1796,7 +1785,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>1</v>
       </c>
@@ -1804,25 +1793,25 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="15">
       <c r="A47" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B47" t="e" cm="1">
-        <f t="array" aca="1" ref="B47" ca="1">_xll.qlHullWhiteProcess(B7,B45,B46)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B47" t="str" cm="1">
+        <f t="array" ref="B47">_xll.qlHullWhiteProcess(B7,B45,B46)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R47C2HullWhiteProcess,A</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15">
       <c r="A49" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B49" t="e" cm="1">
-        <f t="array" aca="1" ref="B49" ca="1">_xll.qlHullWhiteForwardProcess(B7,B45,B46)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B49" t="str" cm="1">
+        <f t="array" ref="B49">_xll.qlHullWhiteForwardProcess(B7,B45,B46)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R49C2HullWhiteForwardProcess,A</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -1830,16 +1819,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>79</v>
       </c>
-      <c r="B51" t="e" cm="1">
-        <f t="array" aca="1" ref="B51" ca="1">_xll.qlHullWhiteForwardProcessSetForwardMeasureTime(B49,B50)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B51" t="b" cm="1">
+        <f t="array" ref="B51">_xll.qlHullWhiteForwardProcessSetForwardMeasureTime(B49,B50)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -1847,7 +1836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1855,34 +1844,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>82</v>
       </c>
-      <c r="B54" t="e" cm="1">
-        <f t="array" aca="1" ref="B54" ca="1">_xll.qlHullWhiteForwardProcessAlpha(B49,B53)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B54" cm="1">
+        <f t="array" ref="B54">_xll.qlHullWhiteForwardProcessAlpha(B49,B53)</f>
+        <v>2.0761142093436498E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>83</v>
       </c>
-      <c r="B55" t="e" cm="1">
-        <f t="array" aca="1" ref="B55" ca="1">_xll.qlHullWhiteForwardProcessB(B49,B52,B53)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B55" cm="1">
+        <f t="array" ref="B55">_xll.qlHullWhiteForwardProcessB(B49,B52,B53)</f>
+        <v>2.9554466451491845</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>84</v>
       </c>
-      <c r="B56" t="e" cm="1">
-        <f t="array" aca="1" ref="B56" ca="1">_xll.qlHullWhiteForwardProcessMT(B49,B52,B53,B53)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B56" cm="1">
+        <f t="array" ref="B56">_xll.qlHullWhiteForwardProcessMT(B49,B52,B53,B53)</f>
+        <v>2.7950927591437191E-4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>85</v>
       </c>
@@ -1890,7 +1879,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>1</v>
       </c>
@@ -1898,7 +1887,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>86</v>
       </c>
@@ -1906,7 +1895,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -1914,7 +1903,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>58</v>
       </c>
@@ -1922,25 +1911,25 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>88</v>
       </c>
-      <c r="B63" t="e" cm="1">
-        <f t="array" aca="1" ref="B63" ca="1">_xll.qlG2Process(B58,B59,B60,B61,B62)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B63" t="str" cm="1">
+        <f t="array" ref="B63">_xll.qlG2Process(B58,B59,B60,B61,B62)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R63C2G2Process,A</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>90</v>
       </c>
-      <c r="B65" t="e" cm="1">
-        <f t="array" aca="1" ref="B65" ca="1">_xll.qlG2ForwardProcess(B58,B59,B60,B61,B62)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B65" t="str" cm="1">
+        <f t="array" ref="B65">_xll.qlG2ForwardProcess(B58,B59,B60,B61,B62)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R65C2G2ForwardProcess,A</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>89</v>
       </c>
@@ -1948,16 +1937,16 @@
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>91</v>
       </c>
-      <c r="B67" t="e" cm="1">
-        <f t="array" aca="1" ref="B67" ca="1">_xll.qlG2ForwardProcessSetForwardMeasureTime(B65,B66)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B67" t="b" cm="1">
+        <f t="array" ref="B67">_xll.qlG2ForwardProcessSetForwardMeasureTime(B65,B66)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>92</v>
       </c>
@@ -1971,7 +1960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>93</v>
       </c>
@@ -1988,7 +1977,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>94</v>
       </c>
@@ -2005,30 +1994,30 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>95</v>
       </c>
-      <c r="B73" t="e" cm="1">
-        <f t="array" aca="1" ref="B73" ca="1">_xll.qlGsrProcess(B70:D70,B71:E71,B72:E72)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B73" t="str" cm="1">
+        <f t="array" ref="B73">_xll.qlGsrProcess(B70:D70,B71:E71,B72:E72)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R73C2GsrProcess,A</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>101</v>
       </c>
-      <c r="B75" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B75" ca="1">FIND("NotImplementedError: NotImplementedError: qlGsrProcessSigma is currently broken", _xll.qlGsrProcessSigma(B73,4))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B75" s="7" cm="1">
+        <f t="array" ref="B75">FIND("NotImplementedError: NotImplementedError: qlGsrProcessSigma is currently broken", _xll.qlGsrProcessSigma(B73,4))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>97</v>
       </c>
@@ -2036,7 +2025,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>98</v>
       </c>
@@ -2044,7 +2033,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>99</v>
       </c>
@@ -2052,7 +2041,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2">
       <c r="A81" t="s">
         <v>100</v>
       </c>
@@ -2060,43 +2049,43 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2">
       <c r="A82" t="s">
         <v>102</v>
       </c>
-      <c r="B82" t="e" cm="1">
-        <f t="array" aca="1" ref="B82" ca="1">_xll.qlOrnsteinUhlenbeckProcess(B78,B79,B80,B81)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B82" t="str" cm="1">
+        <f t="array" ref="B82">_xll.qlOrnsteinUhlenbeckProcess(B78,B79,B80,B81)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R82C2OrnsteinUhlenbeckProcess,A</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83" t="s">
         <v>103</v>
       </c>
-      <c r="B83" t="e" cm="1">
-        <f t="array" aca="1" ref="B83" ca="1">_xll.qlOrnsteinUhlenbeckProcessSpeed(B82)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B83" cm="1">
+        <f t="array" ref="B83">_xll.qlOrnsteinUhlenbeckProcessSpeed(B82)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84" t="s">
         <v>104</v>
       </c>
-      <c r="B84" t="e" cm="1">
-        <f t="array" aca="1" ref="B84" ca="1">_xll.qlOrnsteinUhlenbeckProcessVolatility(B82)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B84" cm="1">
+        <f t="array" ref="B84">_xll.qlOrnsteinUhlenbeckProcessVolatility(B82)</f>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
         <v>105</v>
       </c>
-      <c r="B85" t="e" cm="1">
-        <f t="array" aca="1" ref="B85" ca="1">_xll.qlOrnsteinUhlenbeckProcessLevel(B82)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B85" cm="1">
+        <f t="array" ref="B85">_xll.qlOrnsteinUhlenbeckProcessLevel(B82)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87" t="s">
         <v>106</v>
       </c>
@@ -2104,7 +2093,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2">
       <c r="A88" t="s">
         <v>108</v>
       </c>
@@ -2112,25 +2101,25 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2">
       <c r="A89" t="s">
         <v>107</v>
       </c>
-      <c r="B89" t="e" cm="1">
-        <f t="array" aca="1" ref="B89" ca="1">_xll.qlExtendedOrnsteinUhlenbeckProcessConstantFunction(B87)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B89" t="str" cm="1">
+        <f t="array" ref="B89">_xll.qlExtendedOrnsteinUhlenbeckProcessConstantFunction(B87)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R89C2function,A</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90" t="s">
         <v>109</v>
       </c>
-      <c r="B90" t="e" cm="1">
-        <f t="array" aca="1" ref="B90" ca="1">_xll.qlExtendedOrnsteinUhlenbeckProcess(B78,B79,B80,B89,B88)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B90" t="str" cm="1">
+        <f t="array" ref="B90">_xll.qlExtendedOrnsteinUhlenbeckProcess(B78,B79,B80,B89,B88)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R90C2ExtendedOrnsteinUhlenbeckProcess,A</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92" t="s">
         <v>110</v>
       </c>
@@ -2138,7 +2127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2">
       <c r="A93" t="s">
         <v>111</v>
       </c>
@@ -2146,7 +2135,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2">
       <c r="A94" t="s">
         <v>112</v>
       </c>
@@ -2154,7 +2143,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2">
       <c r="A95" t="s">
         <v>87</v>
       </c>
@@ -2162,16 +2151,16 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2">
       <c r="A96" t="s">
         <v>113</v>
       </c>
-      <c r="B96" t="e" cm="1">
-        <f t="array" aca="1" ref="B96" ca="1">_xll.qlExtOUWithJumpsProcess(B90,B92,B93,B94,B95)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B96" t="str" cm="1">
+        <f t="array" ref="B96">_xll.qlExtOUWithJumpsProcess(B90,B92,B93,B94,B95)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R96C2ExtOUWithJumpsProcess,A</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>58</v>
       </c>
@@ -2179,25 +2168,25 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>114</v>
       </c>
-      <c r="B99" t="e" cm="1">
-        <f t="array" aca="1" ref="B99" ca="1">_xll.qlKlugeExtOUProcess(B98,B96,B90)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B99" t="str" cm="1">
+        <f t="array" ref="B99">_xll.qlKlugeExtOUProcess(B98,B96,B90)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R99C2KlugeExtOUProcess,A</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>8</v>
       </c>
-      <c r="B100" t="e" cm="1">
-        <f t="array" aca="1" ref="B100" ca="1">TRANSPOSE(_xll.qlStochasticProcessInitialValues(B99))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B100" cm="1">
+        <f t="array" ref="B100">TRANSPOSE(_xll.qlStochasticProcessInitialValues(B99))</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
       <c r="A103" t="s">
         <v>56</v>
       </c>
@@ -2211,7 +2200,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5">
       <c r="A104" t="s">
         <v>121</v>
       </c>
@@ -2225,7 +2214,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5">
       <c r="A105" t="s">
         <v>122</v>
       </c>
@@ -2239,7 +2228,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5">
       <c r="A106" t="s">
         <v>111</v>
       </c>
@@ -2253,7 +2242,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5">
       <c r="A107" t="s">
         <v>123</v>
       </c>
@@ -2267,7 +2256,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5">
       <c r="A108" t="s">
         <v>73</v>
       </c>
@@ -2281,7 +2270,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5">
       <c r="A109" t="s">
         <v>124</v>
       </c>
@@ -2292,7 +2281,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5">
       <c r="A110" t="s">
         <v>59</v>
       </c>
@@ -2303,40 +2292,40 @@
         <v>120</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5">
       <c r="A111" t="s">
         <v>131</v>
       </c>
-      <c r="B111" t="e" cm="1">
-        <f t="array" aca="1" ref="B111" ca="1">_xll.qlGJRGARCHProcess(B7,B6,B5,B103,B104,B105,B106,B107,B108,B109,B110)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B111" t="str" cm="1">
+        <f t="array" ref="B111">_xll.qlGJRGARCHProcess(B7,B6,B5,B103,B104,B105,B106,B107,B108,B109,B110)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R111C2GJRGARCHProcess,A</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
       <c r="A112" t="s">
         <v>132</v>
       </c>
-      <c r="B112" t="e" cm="1">
-        <f t="array" aca="1" ref="B112" ca="1">_xll.qlGJRGARCHProcessS0(B111)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B112" cm="1">
+        <f t="array" ref="B112">_xll.qlGJRGARCHProcessS0(B111)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
       <c r="A113" t="s">
         <v>133</v>
       </c>
-      <c r="B113" t="e" cm="1">
-        <f t="array" aca="1" ref="B113" ca="1">_xll.qlGJRGARCHProcessRiskFreeRate(B111)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B113" t="str" cm="1">
+        <f t="array" ref="B113">_xll.qlGJRGARCHProcessRiskFreeRate(B111)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R113C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
       <c r="A114" t="s">
         <v>134</v>
       </c>
-      <c r="B114" t="e" cm="1">
-        <f t="array" aca="1" ref="B114" ca="1">_xll.qlGJRGARCHProcessDividendYield(B111)</f>
-        <v>#VALUE!</v>
+      <c r="B114" t="str" cm="1">
+        <f t="array" ref="B114">_xll.qlGJRGARCHProcessDividendYield(B111)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R114C2YieldTermStructureHandle,A</v>
       </c>
     </row>
   </sheetData>

--- a/tests/workbooktests/workbooks/test_stochasticprocess.xlsx
+++ b/tests/workbooktests/workbooks/test_stochasticprocess.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F967E81-9B61-417A-8653-FE86C21F3EAA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBAB49A-9B90-4E94-9BBF-6FCA7B581B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{536DAD22-F64C-4E0C-9C73-53C6A08A9B53}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{536DAD22-F64C-4E0C-9C73-53C6A08A9B53}"/>
   </bookViews>
   <sheets>
     <sheet name="qlStochasticProcess(1D)" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -30,14 +41,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -52,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="142">
   <si>
     <t>S0</t>
   </si>
@@ -457,13 +468,34 @@
   </si>
   <si>
     <t>qlGJRGARCHProcessDividendYield</t>
+  </si>
+  <si>
+    <t>term_structure</t>
+  </si>
+  <si>
+    <t>qlG2Process with ts</t>
+  </si>
+  <si>
+    <t>qlG2ProcessShortRate</t>
+  </si>
+  <si>
+    <t>qlG2ForwardProcess with ts</t>
+  </si>
+  <si>
+    <t>qlG2ForwardProcessPhi</t>
+  </si>
+  <si>
+    <t>qlG2ForwardProcessShortRate</t>
+  </si>
+  <si>
+    <t>qlG2ProcessPhi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -860,13 +892,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F373020B-96A1-4AED-B897-7871E86B1E67}">
   <dimension ref="A1:C58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.75" customWidth="1"/>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -874,7 +906,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -882,7 +914,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -890,7 +922,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -901,7 +933,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>0.2</v>
       </c>
@@ -909,7 +941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -918,13 +950,13 @@
         <v>欣[test_stochasticprocess.xlsx]qlStochasticProcess(1D)!R8C2GeometricBrownianMotionProcess,A</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" t="str">
         <f t="array" ref="B9">_xll.qlGeometricBrownianMotionProcess(B1,B2,B3)</f>
         <v>欣[test_stochasticprocess.xlsx]qlStochasticProcess(1D)!R9C2GeometricBrownianMotionProcess,A</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -933,7 +965,7 @@
         <v>欣[test_stochasticprocess.xlsx]qlStochasticProcess(1D)!R11C2StochasticProcessArray,A</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -942,7 +974,7 @@
         <v>欣[test_stochasticprocess.xlsx]qlStochasticProcess(1D)!R12C2StochasticProcessArray,A</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -951,7 +983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -960,7 +992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -969,7 +1001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -978,7 +1010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -987,7 +1019,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -996,7 +1028,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1004,7 +1036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -1013,7 +1045,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -1022,16 +1054,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>9</v>
       </c>
       <c r="B27">
-        <f t="array" aca="1" ref="B27" ca="1">TRANSPOSE(_xll.qlStochasticProcessDrift(B12,B23,_xlfn.ANCHORARRAY(B21)))</f>
-        <v>-107341312.95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <f t="array" ref="B27">TRANSPOSE(_xll.qlStochasticProcessDrift(B12,B23,_xlfn.ANCHORARRAY(B21)))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1040,16 +1072,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
       <c r="B30">
-        <f t="array" aca="1" ref="B30" ca="1">_xll.qlStochasticProcessDiffusion(B12,B23,_xlfn.ANCHORARRAY(B21))</f>
-        <v>-332584893.93231082</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <f t="array" ref="B30">_xll.qlStochasticProcessDiffusion(B12,B23,_xlfn.ANCHORARRAY(B21))</f>
+        <v>15.491933384829666</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -1058,16 +1090,16 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>13</v>
       </c>
       <c r="B34">
-        <f t="array" aca="1" ref="B34" ca="1">TRANSPOSE(_xll.qlStochasticProcessExpectation(B12,0,_xlfn.ANCHORARRAY(B21),B23))</f>
-        <v>-2361508884.9000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <f t="array" ref="B34">TRANSPOSE(_xll.qlStochasticProcessExpectation(B12,0,_xlfn.ANCHORARRAY(B21),B23))</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -1076,16 +1108,16 @@
         <v>28.284271247461902</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>14</v>
       </c>
       <c r="B37">
-        <f t="array" aca="1" ref="B37" ca="1">_xll.qlStochasticProcessStdDeviation(B12,0,_xlfn.ANCHORARRAY(B21),B23)</f>
-        <v>-470346067.63949126</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <f t="array" ref="B37">_xll.qlStochasticProcessStdDeviation(B12,0,_xlfn.ANCHORARRAY(B21),B23)</f>
+        <v>21.908902300206645</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -1094,49 +1126,49 @@
         <v>800.00000000000011</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>15</v>
       </c>
       <c r="B41">
-        <f t="array" aca="1" ref="B41" ca="1">_xll.qlStochasticProcessCovariance(B12,0,_xlfn.ANCHORARRAY(B21),B23)</f>
-        <v>3.6870903890655488E+17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <f t="array" ref="B41">_xll.qlStochasticProcessCovariance(B12,0,_xlfn.ANCHORARRAY(B21),B23)</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>16</v>
       </c>
       <c r="B44">
         <f ca="1">2*(RAND()-0.5)</f>
-        <v>0.18331920132897173</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>0.90494203555819341</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B45">
         <f ca="1">2*(RAND()-0.5)</f>
-        <v>-0.30005456652867779</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>0.7381384036631391</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>17</v>
       </c>
       <c r="B47">
         <f t="array" aca="1" ref="B47" ca="1">_xll.qlStochasticProcessEvolve(B11,0,B20,B23,B44)</f>
-        <v>115.18505001525672</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>135.59562599695826</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>17</v>
       </c>
       <c r="B48">
         <f t="array" aca="1" ref="B48" ca="1">TRANSPOSE(_xll.qlStochasticProcessEvolve(B12,0,_xlfn.ANCHORARRAY(B21),B23,B44:B45))</f>
-        <v>-2332500608.0347495</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>143.03050782354626</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -1145,7 +1177,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>19</v>
       </c>
@@ -1154,7 +1186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>20</v>
       </c>
@@ -1163,7 +1195,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>21</v>
       </c>
@@ -1172,7 +1204,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>22</v>
       </c>
@@ -1181,7 +1213,7 @@
         <v>28.284271247461902</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>23</v>
       </c>
@@ -1190,16 +1222,16 @@
         <v>800</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>24</v>
       </c>
       <c r="B57">
         <f t="array" aca="1" ref="B57" ca="1">_xll.qlStochasticProcess1DEvolve(B8,0,B20,B23,B44)</f>
-        <v>115.18505001525672</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>135.59562599695826</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -1216,13 +1248,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF463D5A-8059-46B7-9FB0-FDD57B429219}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.75" customWidth="1"/>
+    <col min="1" max="1" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1230,7 +1262,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1239,7 +1271,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1247,7 +1279,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1255,7 +1287,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -1263,10 +1295,10 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1275,7 +1307,7 @@
         <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R7C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1284,7 +1316,7 @@
         <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R8C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1293,7 +1325,7 @@
         <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R9C2BlackVolTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>30</v>
       </c>
@@ -1302,7 +1334,7 @@
         <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R10C2LocalVolTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -1311,7 +1343,7 @@
         <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R12C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1320,7 +1352,7 @@
         <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R13C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1329,7 +1361,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1338,7 +1370,7 @@
         <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R16C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1347,7 +1379,7 @@
         <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R17C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1356,7 +1388,7 @@
         <v>欣[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R18C2BlackVolTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -1369,7 +1401,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1382,7 +1414,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -1395,7 +1427,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -1408,7 +1440,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -1421,7 +1453,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -1441,14 +1473,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{295C3676-83DD-40B3-9B89-D288ED5DA16F}">
-  <dimension ref="A1:F114"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:F120"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.375" customWidth="1"/>
-    <col min="2" max="2" width="14.75" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1456,7 +1488,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1465,7 +1497,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -1473,7 +1505,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1482,7 +1514,7 @@
         <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R6C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1491,7 +1523,7 @@
         <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R7C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1500,7 +1532,7 @@
         <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R8C2BlackVolTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -1508,7 +1540,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -1516,7 +1548,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -1524,7 +1556,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>46</v>
       </c>
@@ -1533,7 +1565,7 @@
         <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R13C2Merton76Process,A</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1542,7 +1574,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1553,7 +1585,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>52</v>
       </c>
@@ -1561,7 +1593,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -1569,7 +1601,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>55</v>
       </c>
@@ -1578,7 +1610,7 @@
         <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R19C2VarianceGammaProcess,A</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1587,7 +1619,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1595,7 +1627,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1603,7 +1635,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1611,7 +1643,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -1619,7 +1651,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1627,7 +1659,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -1635,7 +1667,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>61</v>
       </c>
@@ -1644,7 +1676,7 @@
         <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R28C2HestonProcess,A</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1653,7 +1685,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1662,7 +1694,7 @@
         <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R30C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1671,7 +1703,7 @@
         <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R31C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1682,7 +1714,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>57</v>
       </c>
@@ -1693,7 +1725,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>53</v>
       </c>
@@ -1704,7 +1736,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>1</v>
       </c>
@@ -1715,7 +1747,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>58</v>
       </c>
@@ -1726,7 +1758,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>73</v>
       </c>
@@ -1737,7 +1769,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -1748,7 +1780,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -1759,7 +1791,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>75</v>
       </c>
@@ -1768,16 +1800,21 @@
         <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R41C2BatesProcess,A</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>8</v>
       </c>
       <c r="B42" cm="1">
-        <f t="array" ref="B42">_xll.qlStochasticProcessInitialValues(B41)</f>
+        <f t="array" ref="B42:B43">_xll.qlStochasticProcessInitialValues(B41)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>76</v>
       </c>
@@ -1785,7 +1822,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1</v>
       </c>
@@ -1793,7 +1830,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>77</v>
       </c>
@@ -1802,7 +1839,7 @@
         <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R47C2HullWhiteProcess,A</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>78</v>
       </c>
@@ -1811,7 +1848,7 @@
         <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R49C2HullWhiteForwardProcess,A</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -1819,7 +1856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -1828,7 +1865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -1836,7 +1873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1844,7 +1881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -1853,7 +1890,7 @@
         <v>2.0761142093436498E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1862,7 +1899,7 @@
         <v>2.9554466451491845</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -1871,7 +1908,7 @@
         <v>2.7950927591437191E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>85</v>
       </c>
@@ -1879,7 +1916,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1</v>
       </c>
@@ -1887,7 +1924,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>86</v>
       </c>
@@ -1895,7 +1932,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -1903,7 +1940,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>58</v>
       </c>
@@ -1911,421 +1948,490 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>135</v>
+      </c>
+      <c r="B63" t="str" cm="1">
+        <f t="array" ref="B63">_xll.qlFlatForward(B1,0.03,"actual365fixed")</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R63C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>88</v>
       </c>
-      <c r="B63" t="str" cm="1">
-        <f t="array" ref="B63">_xll.qlG2Process(B58,B59,B60,B61,B62)</f>
-        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R63C2G2Process,A</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="B64" t="str" cm="1">
+        <f t="array" ref="B64">_xll.qlG2Process(B58,B59,B60,B61,B62)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R64C2G2Process,A</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" t="str" cm="1">
+        <f t="array" ref="B65">_xll.qlG2Process(B58,B59,B60,B61,B62,B63)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R65C2G2Process,A</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" cm="1">
+        <f t="array" ref="B66">_xll.qlG2ProcessPhi(B65,0)</f>
+        <v>2.9999999999267082E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>137</v>
+      </c>
+      <c r="B67" cm="1">
+        <f t="array" ref="B67">_xll.qlG2ProcessShortRate(B65,0,0,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>90</v>
       </c>
-      <c r="B65" t="str" cm="1">
-        <f t="array" ref="B65">_xll.qlG2ForwardProcess(B58,B59,B60,B61,B62)</f>
-        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R65C2G2ForwardProcess,A</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" t="s">
+      <c r="B69" t="str" cm="1">
+        <f t="array" ref="B69">_xll.qlG2ForwardProcess(B58,B59,B60,B61,B62)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R69C2G2ForwardProcess,A</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>89</v>
       </c>
-      <c r="B66">
+      <c r="B70">
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
-      <c r="A67" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>91</v>
       </c>
-      <c r="B67" t="b" cm="1">
-        <f t="array" ref="B67">_xll.qlG2ForwardProcessSetForwardMeasureTime(B65,B66)</f>
+      <c r="B71" t="b" cm="1">
+        <f t="array" ref="B71">_xll.qlG2ForwardProcessSetForwardMeasureTime(B69,B70)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
-      <c r="A70" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>138</v>
+      </c>
+      <c r="B72" t="str" cm="1">
+        <f t="array" ref="B72">_xll.qlG2ForwardProcess(B58,B59,B60,B61,B62,B63)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R72C2G2ForwardProcess,A</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>139</v>
+      </c>
+      <c r="B73" cm="1">
+        <f t="array" ref="B73">_xll.qlG2ForwardProcessPhi(B72,0)</f>
+        <v>2.9999999999267082E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>140</v>
+      </c>
+      <c r="B74" cm="1">
+        <f t="array" ref="B74">_xll.qlG2ForwardProcessShortRate(B72,0,0,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>92</v>
       </c>
-      <c r="B70">
+      <c r="B76">
         <v>2</v>
       </c>
-      <c r="C70">
+      <c r="C76">
         <v>5</v>
       </c>
-      <c r="D70">
+      <c r="D76">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
-      <c r="A71" t="s">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>93</v>
       </c>
-      <c r="B71">
+      <c r="B77">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C71">
+      <c r="C77">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="D71">
+      <c r="D77">
         <v>0.01</v>
       </c>
-      <c r="E71">
+      <c r="E77">
         <v>0.01</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
-      <c r="A72" t="s">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>94</v>
       </c>
-      <c r="B72" s="6">
+      <c r="B78" s="6">
         <v>0.03</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C78" s="6">
         <v>0.03</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D78" s="6">
         <v>0.03</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E78" s="6">
         <v>0.03</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
-      <c r="A73" t="s">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>95</v>
       </c>
-      <c r="B73" t="str" cm="1">
-        <f t="array" ref="B73">_xll.qlGsrProcess(B70:D70,B71:E71,B72:E72)</f>
-        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R73C2GsrProcess,A</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="7" t="s">
+      <c r="B79" t="str" cm="1">
+        <f t="array" ref="B79">_xll.qlGsrProcess(B76:D76,B77:E77,B78:E78)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R79C2GsrProcess,A</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
-      <c r="A75" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>101</v>
       </c>
-      <c r="B75" s="7" cm="1">
-        <f t="array" ref="B75">FIND("NotImplementedError: NotImplementedError: qlGsrProcessSigma is currently broken", _xll.qlGsrProcessSigma(B73,4))</f>
+      <c r="B81" s="7" cm="1">
+        <f t="array" ref="B81">FIND("NotImplementedError: NotImplementedError: qlGsrProcessSigma is currently broken", _xll.qlGsrProcessSigma(B79,4))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
-      <c r="A78" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>97</v>
       </c>
-      <c r="B78">
+      <c r="B84">
         <v>0.1</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
-      <c r="A79" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>98</v>
       </c>
-      <c r="B79">
+      <c r="B85">
         <v>0.01</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
-      <c r="A80" t="s">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>99</v>
       </c>
-      <c r="B80">
+      <c r="B86">
         <v>0.03</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
-      <c r="A81" t="s">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>100</v>
       </c>
-      <c r="B81">
+      <c r="B87">
         <v>0.04</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
-      <c r="A82" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>102</v>
       </c>
-      <c r="B82" t="str" cm="1">
-        <f t="array" ref="B82">_xll.qlOrnsteinUhlenbeckProcess(B78,B79,B80,B81)</f>
-        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R82C2OrnsteinUhlenbeckProcess,A</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" t="s">
+      <c r="B88" t="str" cm="1">
+        <f t="array" ref="B88">_xll.qlOrnsteinUhlenbeckProcess(B84,B85,B86,B87)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R88C2OrnsteinUhlenbeckProcess,A</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>103</v>
       </c>
-      <c r="B83" cm="1">
-        <f t="array" ref="B83">_xll.qlOrnsteinUhlenbeckProcessSpeed(B82)</f>
+      <c r="B89" cm="1">
+        <f t="array" ref="B89">_xll.qlOrnsteinUhlenbeckProcessSpeed(B88)</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
-      <c r="A84" t="s">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>104</v>
       </c>
-      <c r="B84" cm="1">
-        <f t="array" ref="B84">_xll.qlOrnsteinUhlenbeckProcessVolatility(B82)</f>
+      <c r="B90" cm="1">
+        <f t="array" ref="B90">_xll.qlOrnsteinUhlenbeckProcessVolatility(B88)</f>
         <v>0.01</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
-      <c r="A85" t="s">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>105</v>
       </c>
-      <c r="B85" cm="1">
-        <f t="array" ref="B85">_xll.qlOrnsteinUhlenbeckProcessLevel(B82)</f>
+      <c r="B91" cm="1">
+        <f t="array" ref="B91">_xll.qlOrnsteinUhlenbeckProcessLevel(B88)</f>
         <v>0.04</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
-      <c r="A87" t="s">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>106</v>
       </c>
-      <c r="B87">
+      <c r="B93">
         <v>0.01</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
-      <c r="A88" t="s">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>108</v>
       </c>
-      <c r="B88" s="8">
+      <c r="B94" s="8">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
-      <c r="A89" t="s">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>107</v>
       </c>
-      <c r="B89" t="str" cm="1">
-        <f t="array" ref="B89">_xll.qlExtendedOrnsteinUhlenbeckProcessConstantFunction(B87)</f>
-        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R89C2function,A</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" t="s">
+      <c r="B95" t="str" cm="1">
+        <f t="array" ref="B95">_xll.qlExtendedOrnsteinUhlenbeckProcessConstantFunction(B93)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R95C2function,A</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>109</v>
       </c>
-      <c r="B90" t="str" cm="1">
-        <f t="array" ref="B90">_xll.qlExtendedOrnsteinUhlenbeckProcess(B78,B79,B80,B89,B88)</f>
-        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R90C2ExtendedOrnsteinUhlenbeckProcess,A</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" t="s">
+      <c r="B96" t="str" cm="1">
+        <f t="array" ref="B96">_xll.qlExtendedOrnsteinUhlenbeckProcess(B84,B85,B86,B95,B94)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R96C2ExtendedOrnsteinUhlenbeckProcess,A</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>110</v>
       </c>
-      <c r="B92">
+      <c r="B98">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
-      <c r="A93" t="s">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>111</v>
       </c>
-      <c r="B93">
+      <c r="B99">
         <v>0.5</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
-      <c r="A94" t="s">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>112</v>
       </c>
-      <c r="B94">
+      <c r="B100">
         <v>0.1</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
-      <c r="A95" t="s">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>87</v>
       </c>
-      <c r="B95">
+      <c r="B101">
         <v>0.2</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
-      <c r="A96" t="s">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>113</v>
       </c>
-      <c r="B96" t="str" cm="1">
-        <f t="array" ref="B96">_xll.qlExtOUWithJumpsProcess(B90,B92,B93,B94,B95)</f>
-        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R96C2ExtOUWithJumpsProcess,A</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" t="s">
+      <c r="B102" t="str" cm="1">
+        <f t="array" ref="B102">_xll.qlExtOUWithJumpsProcess(B96,B98,B99,B100,B101)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R102C2ExtOUWithJumpsProcess,A</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>58</v>
       </c>
-      <c r="B98">
+      <c r="B104">
         <v>0.5</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
-      <c r="A99" t="s">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>114</v>
       </c>
-      <c r="B99" t="str" cm="1">
-        <f t="array" ref="B99">_xll.qlKlugeExtOUProcess(B98,B96,B90)</f>
-        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R99C2KlugeExtOUProcess,A</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" t="s">
+      <c r="B105" t="str" cm="1">
+        <f t="array" ref="B105">_xll.qlKlugeExtOUProcess(B104,B102,B96)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R105C2KlugeExtOUProcess,A</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>8</v>
       </c>
-      <c r="B100" cm="1">
-        <f t="array" ref="B100">TRANSPOSE(_xll.qlStochasticProcessInitialValues(B99))</f>
+      <c r="B106" cm="1">
+        <f t="array" ref="B106:D106">TRANSPOSE(_xll.qlStochasticProcessInitialValues(B105))</f>
         <v>0.03</v>
       </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" t="s">
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="D106">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>56</v>
       </c>
-      <c r="B103">
+      <c r="B109">
         <v>0.04</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C109" t="s">
         <v>125</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E109" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
-      <c r="A104" t="s">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>121</v>
       </c>
-      <c r="B104">
+      <c r="B110">
         <v>0.1</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C110" t="s">
         <v>126</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E110" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
-      <c r="A105" t="s">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>122</v>
       </c>
-      <c r="B105">
+      <c r="B111">
         <v>0.05</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C111" t="s">
         <v>127</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E111" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
-      <c r="A106" t="s">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>111</v>
       </c>
-      <c r="B106">
+      <c r="B112">
         <v>0.9</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C112" t="s">
         <v>128</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E112" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
-      <c r="A107" t="s">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>123</v>
       </c>
-      <c r="B107">
+      <c r="B113">
         <v>0.1</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C113" t="s">
         <v>126</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E113" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
-      <c r="A108" t="s">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>73</v>
       </c>
-      <c r="B108">
+      <c r="B114">
         <v>0.2</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C114" t="s">
         <v>129</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E114" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
-      <c r="A109" t="s">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>124</v>
       </c>
-      <c r="B109">
+      <c r="B115">
         <v>252</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E115" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
-      <c r="A110" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>59</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B116" t="s">
         <v>130</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E116" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
-      <c r="A111" t="s">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>131</v>
       </c>
-      <c r="B111" t="str" cm="1">
-        <f t="array" ref="B111">_xll.qlGJRGARCHProcess(B7,B6,B5,B103,B104,B105,B106,B107,B108,B109,B110)</f>
-        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R111C2GJRGARCHProcess,A</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" t="s">
+      <c r="B117" t="str" cm="1">
+        <f t="array" ref="B117">_xll.qlGJRGARCHProcess(B7,B6,B5,B109,B110,B111,B112,B113,B114,B115,B116)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R117C2GJRGARCHProcess,A</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>132</v>
       </c>
-      <c r="B112" cm="1">
-        <f t="array" ref="B112">_xll.qlGJRGARCHProcessS0(B111)</f>
+      <c r="B118" cm="1">
+        <f t="array" ref="B118">_xll.qlGJRGARCHProcessS0(B117)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
-      <c r="A113" t="s">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>133</v>
       </c>
-      <c r="B113" t="str" cm="1">
-        <f t="array" ref="B113">_xll.qlGJRGARCHProcessRiskFreeRate(B111)</f>
-        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R113C2YieldTermStructureHandle,A</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" t="s">
+      <c r="B119" t="str" cm="1">
+        <f t="array" ref="B119">_xll.qlGJRGARCHProcessRiskFreeRate(B117)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R119C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>134</v>
       </c>
-      <c r="B114" t="str" cm="1">
-        <f t="array" ref="B114">_xll.qlGJRGARCHProcessDividendYield(B111)</f>
-        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R114C2YieldTermStructureHandle,A</v>
+      <c r="B120" t="str" cm="1">
+        <f t="array" ref="B120">_xll.qlGJRGARCHProcessDividendYield(B117)</f>
+        <v>欣[test_stochasticprocess.xlsx]StochasticProcesses!R120C2YieldTermStructureHandle,A</v>
       </c>
     </row>
   </sheetData>
